--- a/Result/profitability/8069.xlsx
+++ b/Result/profitability/8069.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>2.115</v>
+        <v>2.3</v>
       </c>
       <c r="N2" t="n">
-        <v>49.945</v>
+        <v>51.23375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.21</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9225</v>
+        <v>1.94125</v>
       </c>
       <c r="N3" t="n">
-        <v>46.1325</v>
+        <v>46.75375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>1.46</v>
+        <v>1.625</v>
       </c>
       <c r="N4" t="n">
-        <v>39.31</v>
+        <v>40.12375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05375</v>
+        <v>1.135</v>
       </c>
       <c r="N5" t="n">
-        <v>31.6925</v>
+        <v>31.49625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6024999999999999</v>
+        <v>0.5475</v>
       </c>
       <c r="N6" t="n">
-        <v>22.1625</v>
+        <v>22.50625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03124999999999996</v>
+        <v>0.31375</v>
       </c>
       <c r="N7" t="n">
-        <v>14.62875</v>
+        <v>15.92875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08125000000000004</v>
+        <v>0.02124999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>9.862500000000001</v>
+        <v>9.74625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3412500000000001</v>
+        <v>-0.34125</v>
       </c>
       <c r="N9" t="n">
         <v>4.09125</v>
@@ -1772,7 +1772,7 @@
         <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2650000000000001</v>
+        <v>-0.265</v>
       </c>
       <c r="N11" t="n">
         <v>7.985000000000001</v>
@@ -1899,7 +1899,7 @@
         <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1037500000000001</v>
+        <v>-0.10375</v>
       </c>
       <c r="N12" t="n">
         <v>12.19</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10216</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4217</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5999</v>
+      </c>
+      <c r="F75" t="n">
+        <v>58.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3542</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1033</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4575</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3733</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N75" t="n">
+        <v>54.665</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8199999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3402489626556016</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01559094719195309</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.251937984496124</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02604080278653176</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
